--- a/levels/Levels.xlsx
+++ b/levels/Levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computer\Documents\Coding Environment\Old Python\btp-bls(CE)\levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A168BD-E5E5-404D-8DEE-B685F1D1C724}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEBBD12-89D9-4E2C-9C52-C048D0B8347B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Levels.xlsx" sheetId="1" r:id="rId1"/>
